--- a/TASKS/MP-251/test_import_file.xlsx
+++ b/TASKS/MP-251/test_import_file.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">Beckers</t>
   </si>
   <si>
-    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ -&gt; БЛЕНДЕРЫ БАРНЫЕ</t>
+    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/БЛЕНДЕРЫ БАРНЫЕ</t>
   </si>
   <si>
     <t xml:space="preserve">Япония</t>
@@ -148,7 +148,7 @@
     <t xml:space="preserve">Sottoriva</t>
   </si>
   <si>
-    <t xml:space="preserve">ХОЛОДИЛЬНОЕ ОБОРУДОВАНИЕ -&gt; ШКАФЫ ВИННЫЕ</t>
+    <t xml:space="preserve">ХОЛОДИЛЬНОЕ ОБОРУДОВАНИЕ/ШКАФЫ ВИННЫЕ</t>
   </si>
   <si>
     <t xml:space="preserve">Казахстан</t>
@@ -202,13 +202,13 @@
     <t xml:space="preserve">TATRA </t>
   </si>
   <si>
-    <t xml:space="preserve">ПОСУДА И ИНВЕНТАРЬ -&gt; ФАРФОР, КЕРАМИКА -&gt; 04.01.06. PORDAMSA -&gt; 04.01.06.20. CASUAL</t>
+    <t xml:space="preserve">ПОСУДА И ИНВЕНТАРЬ/ФАРФОР, КЕРАМИКА/04.01.06. PORDAMSA/04.01.06.20. CASUAL</t>
   </si>
   <si>
     <t xml:space="preserve">Аландские острова</t>
   </si>
   <si>
-    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ -&gt; АКСЕССУАРЫ ДЛЯ БАРНОГО ОБОРУДОВАНИЯ -&gt; ДИСПЕНСЕРЫ</t>
+    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/АКСЕССУАРЫ ДЛЯ БАРНОГО ОБОРУДОВАНИЯ/ДИСПЕНСЕРЫ</t>
   </si>
   <si>
     <t xml:space="preserve">HKN-PE34Rк</t>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">HKN-PE34R4</t>
   </si>
   <si>
-    <t xml:space="preserve">ОБОРУДОВАНИЕ ДЛЯ FAST FOOD -&gt; ГРИЛИ КОНТАКТНЫЕ</t>
+    <t xml:space="preserve">ОБОРУДОВАНИЕ ДЛЯ FAST FOOD/ГРИЛИ КОНТАКТНЫЕ</t>
   </si>
   <si>
     <t xml:space="preserve">Сербия</t>
@@ -349,7 +349,7 @@
     <t xml:space="preserve">COLDLINE</t>
   </si>
   <si>
-    <t xml:space="preserve">ТЕПЛОВОЕ ОБОРУДОВАНИЕ -&gt; КОТЛЫ ПИЩЕВАРОЧНЫЕ ДЛЯ ТЕПЛОВЫХ ЛИНИЙ</t>
+    <t xml:space="preserve">ТЕПЛОВОЕ ОБОРУДОВАНИЕ/КОТЛЫ ПИЩЕВАРОЧНЫЕ ДЛЯ ТЕПЛОВЫХ ЛИНИЙ</t>
   </si>
   <si>
     <t xml:space="preserve">ПАРОКОНВЕКТОМАТ</t>
@@ -421,7 +421,7 @@
     <t xml:space="preserve">KOTEYKA</t>
   </si>
   <si>
-    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ -&gt; ИЗМЕЛЬЧИТЕЛИ ЛЬДА</t>
+    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/ИЗМЕЛЬЧИТЕЛИ ЛЬДА</t>
   </si>
   <si>
     <t xml:space="preserve">Сент-Люсия</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">ACB5325B W333</t>
   </si>
   <si>
-    <t xml:space="preserve">ОБОРУДОВАНИЕ ДЛЯ FAST FOOD -&gt; БЛИННИЦЫ</t>
+    <t xml:space="preserve">ОБОРУДОВАНИЕ ДЛЯ FAST FOOD/БЛИННИЦЫ</t>
   </si>
   <si>
     <t xml:space="preserve">ACB5325B W444</t>
@@ -457,7 +457,7 @@
     <t xml:space="preserve">Плоские перфорированные алюминиевые противни с бортом 2 см. стандарт</t>
   </si>
   <si>
-    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ -&gt; АППАРАТЫ ДЛЯ ОХЛАЖДЕНИЯ БОКАЛОВ</t>
+    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/АППАРАТЫ ДЛЯ ОХЛАЖДЕНИЯ БОКАЛОВ</t>
   </si>
   <si>
     <t xml:space="preserve">ТЕСТОДЕЛИТЕЛЬ SOTTORIVA АВТОМАТИЧЕСКИЙ ZERO 6/123</t>
@@ -565,7 +565,7 @@
     <t xml:space="preserve">N-ACB5325B W</t>
   </si>
   <si>
-    <t xml:space="preserve">ЭЛЕКТРОМЕХАНИЧЕСКОЕ ОБОРУДОВАНИЕ -&gt; ФАРШЕМЕШАЛКИ</t>
+    <t xml:space="preserve">ЭЛЕКТРОМЕХАНИЧЕСКОЕ ОБОРУДОВАНИЕ/ФАРШЕМЕШАЛКИ</t>
   </si>
   <si>
     <t xml:space="preserve">HKN-PE34RSOS</t>
@@ -584,6 +584,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -643,8 +644,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -670,2833 +675,2836 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P61"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="80.86"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>1.99</v>
       </c>
-      <c r="K2" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L2" s="0" t="n">
+      <c r="K2" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>198.86</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <f aca="false">L2-(L2*0.1)</f>
         <v>178.974</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>35004.24</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <f aca="false">L3-(L3*0.1)</f>
         <v>31503.816</v>
       </c>
-      <c r="N3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="0" t="n">
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>1835</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="K4" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L4" s="0" t="n">
+      <c r="K4" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L4" s="1" t="n">
         <v>89607.03</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <f aca="false">L4-(L4*0.1)</f>
         <v>80646.327</v>
       </c>
-      <c r="N4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="0" t="n">
+      <c r="N4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="1" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="I5" s="0" t="n">
+      <c r="H5" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>440</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="K5" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L5" s="0" t="n">
+      <c r="K5" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>28498.02</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <f aca="false">L5-(L5*0.1)</f>
         <v>25648.218</v>
       </c>
-      <c r="N5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="0" t="n">
+      <c r="N5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>205</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>510</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="K6" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L6" s="0" t="n">
+      <c r="K6" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>57.84</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <f aca="false">L6-(L6*0.1)</f>
         <v>52.056</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="N6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <f aca="false">L7-(L7*0.1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="2" t="n">
         <f aca="false">L8-(L8*0.1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="2" t="n">
         <f aca="false">L9-(L9*0.1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="2" t="n">
         <f aca="false">L10-(L10*0.1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>1780</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>1035</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>845</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>4748.76</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="2" t="n">
         <f aca="false">L11-(L11*0.1)</f>
         <v>4273.884</v>
       </c>
-      <c r="N11" s="0" t="s">
+      <c r="N11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="2" t="n">
         <f aca="false">L12-(L12*0.1)</f>
         <v>900</v>
       </c>
-      <c r="N12" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P12" s="0" t="n">
+      <c r="N12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>460</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <v>460</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="I13" s="1" t="n">
         <v>375</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K13" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L13" s="0" t="n">
+      <c r="K13" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>7994.27</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="2" t="n">
         <f aca="false">L13-(L13*0.1)</f>
         <v>7194.843</v>
       </c>
-      <c r="N13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" s="0" t="n">
+      <c r="N13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>690</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="P13" s="1" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="I14" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J14" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K14" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L14" s="0" t="n">
+      <c r="K14" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="2" t="n">
         <f aca="false">L14-(L14*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N14" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="0" t="n">
+      <c r="N14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <v>410</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="I15" s="0" t="n">
+      <c r="I15" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="J15" s="1" t="n">
         <v>45414</v>
       </c>
-      <c r="K15" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L15" s="0" t="n">
+      <c r="K15" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L15" s="1" t="n">
         <v>26708.04</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="2" t="n">
         <f aca="false">L15-(L15*0.1)</f>
         <v>24037.236</v>
       </c>
-      <c r="N15" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" s="0" t="n">
+      <c r="N15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15" s="1" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I16" s="0" t="n">
+      <c r="I16" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J16" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K16" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L16" s="0" t="n">
+      <c r="K16" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="2" t="n">
         <f aca="false">L16-(L16*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N16" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="0" t="n">
+      <c r="N16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K17" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L17" s="0" t="n">
+      <c r="K17" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L17" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="2" t="n">
         <f aca="false">L17-(L17*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N17" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="0" t="n">
+      <c r="N17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="I18" s="0" t="n">
+      <c r="I18" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="J18" s="0" t="n">
+      <c r="J18" s="1" t="n">
         <v>1.99</v>
       </c>
-      <c r="K18" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L18" s="0" t="n">
+      <c r="K18" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>198.86</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="2" t="n">
         <f aca="false">L18-(L18*0.1)</f>
         <v>178.974</v>
       </c>
-      <c r="N18" s="0" t="s">
+      <c r="N18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I19" s="0" t="n">
+      <c r="I19" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J19" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K19" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L19" s="0" t="n">
+      <c r="K19" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="2" t="n">
         <f aca="false">L19-(L19*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N19" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O19" s="0" t="n">
+      <c r="N19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="P19" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="I20" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="1" t="n">
         <v>35004.24</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="2" t="n">
         <f aca="false">L20-(L20*0.1)</f>
         <v>31503.816</v>
       </c>
-      <c r="N20" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="0" t="n">
+      <c r="N20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <v>1835</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="I21" s="0" t="n">
+      <c r="I21" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J21" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="K21" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L21" s="0" t="n">
+      <c r="K21" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>89607.03</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="2" t="n">
         <f aca="false">L21-(L21*0.1)</f>
         <v>80646.327</v>
       </c>
-      <c r="N21" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="0" t="n">
+      <c r="N21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="P21" s="1" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="H22" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="I22" s="0" t="n">
+      <c r="H22" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>440</v>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="J22" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="K22" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L22" s="0" t="n">
+      <c r="K22" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>28498.02</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" s="2" t="n">
         <f aca="false">L22-(L22*0.1)</f>
         <v>25648.218</v>
       </c>
-      <c r="N22" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="0" t="n">
+      <c r="N22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23" s="1" t="n">
         <v>205</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="I23" s="0" t="n">
+      <c r="I23" s="1" t="n">
         <v>510</v>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J23" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="K23" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L23" s="0" t="n">
+      <c r="K23" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L23" s="1" t="n">
         <v>57.84</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M23" s="2" t="n">
         <f aca="false">L23-(L23*0.1)</f>
         <v>52.056</v>
       </c>
-      <c r="N23" s="0" t="s">
+      <c r="N23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O23" s="0" t="n">
+      <c r="O23" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="1" t="n">
         <v>497</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="1" t="n">
         <v>592</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="I24" s="1" t="n">
         <v>887</v>
       </c>
-      <c r="J24" s="0" t="n">
+      <c r="J24" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="K24" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L24" s="0" t="n">
+      <c r="K24" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>151889.52</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="2" t="n">
         <f aca="false">L24-(L24*0.1)</f>
         <v>136700.568</v>
       </c>
-      <c r="N24" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P24" s="0" t="n">
+      <c r="N24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="1" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="1" t="n">
         <v>535</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="I25" s="0" t="n">
+      <c r="I25" s="1" t="n">
         <v>910</v>
       </c>
-      <c r="J25" s="0" t="n">
+      <c r="J25" s="1" t="n">
         <v>0.69</v>
       </c>
-      <c r="K25" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L25" s="0" t="n">
+      <c r="K25" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>1735.5</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M25" s="2" t="n">
         <f aca="false">L25-(L25*0.1)</f>
         <v>1561.95</v>
       </c>
-      <c r="N25" s="0" t="s">
+      <c r="N25" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="1" t="n">
         <v>697</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="1" t="n">
         <v>710</v>
       </c>
-      <c r="I26" s="0" t="n">
+      <c r="I26" s="1" t="n">
         <v>1960</v>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="J26" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="K26" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26" s="1" t="n">
         <v>35868.7</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M26" s="2" t="n">
         <f aca="false">L26-(L26*0.1)</f>
         <v>32281.83</v>
       </c>
-      <c r="N26" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P26" s="0" t="n">
+      <c r="N26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="1" t="n">
         <v>132</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <v>610</v>
       </c>
-      <c r="I27" s="0" t="n">
+      <c r="I27" s="1" t="n">
         <v>630</v>
       </c>
-      <c r="J27" s="0" t="n">
+      <c r="J27" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="K27" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="1" t="n">
         <v>561941.4</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="M27" s="2" t="n">
         <f aca="false">L27-(L27*0.1)</f>
         <v>505747.26</v>
       </c>
-      <c r="N27" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O27" s="0" t="n">
+      <c r="N27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O27" s="1" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="1" t="n">
         <v>480</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <v>560</v>
       </c>
-      <c r="I28" s="0" t="n">
+      <c r="I28" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="J28" s="0" t="n">
+      <c r="J28" s="1" t="n">
         <v>3.6</v>
       </c>
-      <c r="K28" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L28" s="0" t="n">
+      <c r="K28" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L28" s="1" t="n">
         <v>31287.24</v>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="M28" s="2" t="n">
         <f aca="false">L28-(L28*0.1)</f>
         <v>28158.516</v>
       </c>
-      <c r="N28" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P28" s="0" t="n">
+      <c r="N28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="1" t="n">
         <v>67</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29" s="1" t="n">
         <v>1777</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="I29" s="0" t="n">
+      <c r="I29" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="J29" s="0" t="n">
+      <c r="J29" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="K29" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L29" s="0" t="n">
+      <c r="K29" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L29" s="1" t="n">
         <v>80678.67</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="M29" s="2" t="n">
         <f aca="false">L29-(L29*0.1)</f>
         <v>72610.803</v>
       </c>
-      <c r="N29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O29" s="0" t="n">
+      <c r="N29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O29" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="P29" s="0" t="n">
+      <c r="P29" s="1" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="1" t="n">
         <v>1300</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="I30" s="0" t="n">
+      <c r="I30" s="1" t="n">
         <v>950</v>
       </c>
-      <c r="J30" s="0" t="n">
+      <c r="J30" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="K30" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L30" s="0" t="n">
+      <c r="K30" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L30" s="1" t="n">
         <v>627500.25</v>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="M30" s="2" t="n">
         <f aca="false">L30-(L30*0.1)</f>
         <v>564750.225</v>
       </c>
-      <c r="N30" s="0" t="s">
+      <c r="N30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G31" s="0" t="n">
+      <c r="G31" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="1" t="n">
         <v>840</v>
       </c>
-      <c r="I31" s="0" t="n">
+      <c r="I31" s="1" t="n">
         <v>1055</v>
       </c>
-      <c r="J31" s="0" t="n">
+      <c r="J31" s="1" t="n">
         <v>12.5</v>
       </c>
-      <c r="K31" s="0" t="n">
+      <c r="K31" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L31" s="0" t="n">
+      <c r="L31" s="1" t="n">
         <v>280566.67</v>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="M31" s="2" t="n">
         <f aca="false">L31-(L31*0.1)</f>
         <v>252510.003</v>
       </c>
-      <c r="N31" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O31" s="0" t="n">
+      <c r="N31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O31" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P31" s="0" t="n">
+      <c r="P31" s="1" t="n">
         <v>115</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="G32" s="1" t="n">
         <v>1050</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="1" t="n">
         <v>895</v>
       </c>
-      <c r="I32" s="0" t="n">
+      <c r="I32" s="1" t="n">
         <v>860</v>
       </c>
-      <c r="J32" s="0" t="n">
+      <c r="J32" s="1" t="n">
         <v>16.8</v>
       </c>
-      <c r="K32" s="0" t="n">
+      <c r="K32" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L32" s="0" t="n">
+      <c r="L32" s="1" t="n">
         <v>48238.41</v>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="M32" s="2" t="n">
         <f aca="false">L32-(L32*0.1)</f>
         <v>43414.569</v>
       </c>
-      <c r="N32" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P32" s="0" t="n">
+      <c r="N32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" s="1" t="n">
         <v>115</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="1" t="n">
         <v>216</v>
       </c>
-      <c r="I33" s="0" t="n">
+      <c r="I33" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="J33" s="0" t="n">
+      <c r="J33" s="1" t="n">
         <v>1.19</v>
       </c>
-      <c r="K33" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L33" s="0" t="n">
+      <c r="K33" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L33" s="1" t="n">
         <v>341.94</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="M33" s="2" t="n">
         <f aca="false">L33-(L33*0.1)</f>
         <v>307.746</v>
       </c>
-      <c r="N33" s="0" t="s">
+      <c r="N33" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="1" t="n">
         <v>310</v>
       </c>
-      <c r="I34" s="0" t="n">
+      <c r="I34" s="1" t="n">
         <v>420</v>
       </c>
-      <c r="J34" s="0" t="n">
+      <c r="J34" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="K34" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L34" s="0" t="n">
+      <c r="K34" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>187.98</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="M34" s="2" t="n">
         <f aca="false">L34-(L34*0.1)</f>
         <v>169.182</v>
       </c>
-      <c r="N34" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O34" s="0" t="n">
+      <c r="N34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G35" s="0" t="n">
+      <c r="G35" s="1" t="n">
         <v>460</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="1" t="n">
         <v>460</v>
       </c>
-      <c r="I35" s="0" t="n">
+      <c r="I35" s="1" t="n">
         <v>375</v>
       </c>
-      <c r="J35" s="0" t="n">
+      <c r="J35" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L35" s="0" t="n">
+      <c r="K35" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L35" s="1" t="n">
         <v>7994.27</v>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="M35" s="2" t="n">
         <f aca="false">L35-(L35*0.1)</f>
         <v>7194.843</v>
       </c>
-      <c r="N35" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O35" s="0" t="n">
+      <c r="N35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>690</v>
       </c>
-      <c r="P35" s="0" t="n">
+      <c r="P35" s="1" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="0" t="n">
+      <c r="G36" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="I36" s="0" t="n">
+      <c r="I36" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="J36" s="0" t="n">
+      <c r="J36" s="1" t="n">
         <v>1.99</v>
       </c>
-      <c r="K36" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L36" s="0" t="n">
+      <c r="K36" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>198.86</v>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="M36" s="2" t="n">
         <f aca="false">L36-(L36*0.1)</f>
         <v>178.974</v>
       </c>
-      <c r="N36" s="0" t="s">
+      <c r="N36" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G37" s="0" t="n">
+      <c r="G37" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I37" s="0" t="n">
+      <c r="I37" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J37" s="0" t="n">
+      <c r="J37" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K37" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L37" s="0" t="n">
+      <c r="K37" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="M37" s="2" t="n">
         <f aca="false">L37-(L37*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N37" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O37" s="0" t="n">
+      <c r="N37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P37" s="0" t="n">
+      <c r="P37" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I38" s="0" t="n">
+      <c r="I38" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J38" s="0" t="n">
+      <c r="J38" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K38" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L38" s="0" t="n">
+      <c r="K38" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="M38" s="2" t="n">
         <f aca="false">L38-(L38*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N38" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O38" s="0" t="n">
+      <c r="N38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P38" s="0" t="n">
+      <c r="P38" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G39" s="0" t="n">
+      <c r="G39" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="I39" s="0" t="n">
+      <c r="I39" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="J39" s="0" t="n">
+      <c r="J39" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K39" s="0" t="n">
+      <c r="K39" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L39" s="0" t="n">
+      <c r="L39" s="1" t="n">
         <v>1234</v>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="M39" s="2" t="n">
         <f aca="false">L39-(L39*0.1)</f>
         <v>1110.6</v>
       </c>
-      <c r="N39" s="0" t="s">
+      <c r="N39" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="O39" s="0" t="n">
+      <c r="O39" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="P39" s="0" t="n">
+      <c r="P39" s="1" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G40" s="0" t="n">
+      <c r="G40" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="I40" s="0" t="n">
+      <c r="I40" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="J40" s="0" t="n">
+      <c r="J40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K40" s="0" t="n">
+      <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L40" s="0" t="n">
+      <c r="L40" s="1" t="n">
         <v>1234</v>
       </c>
-      <c r="M40" s="1" t="n">
+      <c r="M40" s="2" t="n">
         <f aca="false">L40-(L40*0.1)</f>
         <v>1110.6</v>
       </c>
-      <c r="N40" s="0" t="s">
+      <c r="N40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="O40" s="0" t="n">
+      <c r="O40" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="P40" s="0" t="n">
+      <c r="P40" s="1" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G41" s="1" t="n">
         <v>497</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="1" t="n">
         <v>592</v>
       </c>
-      <c r="I41" s="0" t="n">
+      <c r="I41" s="1" t="n">
         <v>887</v>
       </c>
-      <c r="J41" s="0" t="n">
+      <c r="J41" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="K41" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L41" s="0" t="n">
+      <c r="K41" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>151889.52</v>
       </c>
-      <c r="M41" s="1" t="n">
+      <c r="M41" s="2" t="n">
         <f aca="false">L41-(L41*0.1)</f>
         <v>136700.568</v>
       </c>
-      <c r="N41" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P41" s="0" t="n">
+      <c r="N41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="1" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="1" t="n">
         <v>497</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="1" t="n">
         <v>592</v>
       </c>
-      <c r="I42" s="0" t="n">
+      <c r="I42" s="1" t="n">
         <v>887</v>
       </c>
-      <c r="J42" s="0" t="n">
+      <c r="J42" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="K42" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L42" s="0" t="n">
+      <c r="K42" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L42" s="1" t="n">
         <v>151889.52</v>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="M42" s="2" t="n">
         <f aca="false">L42-(L42*0.1)</f>
         <v>136700.568</v>
       </c>
-      <c r="N42" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P42" s="0" t="n">
+      <c r="N42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P42" s="1" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="1" t="n">
         <v>136021</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="I43" s="0" t="n">
+      <c r="I43" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="J43" s="0" t="n">
+      <c r="J43" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="K43" s="0" t="n">
+      <c r="K43" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="L43" s="0" t="n">
+      <c r="L43" s="1" t="n">
         <v>5258.82</v>
       </c>
-      <c r="M43" s="1" t="n">
+      <c r="M43" s="2" t="n">
         <f aca="false">L43-(L43*0.1)</f>
         <v>4732.938</v>
       </c>
-      <c r="N43" s="0" t="s">
+      <c r="N43" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G44" s="0" t="n">
+      <c r="G44" s="1" t="n">
         <v>1360</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <v>1760</v>
       </c>
-      <c r="I44" s="0" t="n">
+      <c r="I44" s="1" t="n">
         <v>1750</v>
       </c>
-      <c r="J44" s="0" t="n">
+      <c r="J44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K44" s="0" t="n">
+      <c r="K44" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L44" s="0" t="n">
+      <c r="L44" s="1" t="n">
         <v>4748.76</v>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="M44" s="2" t="n">
         <f aca="false">L44-(L44*0.1)</f>
         <v>4273.884</v>
       </c>
-      <c r="N44" s="0" t="s">
+      <c r="N44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O44" s="0" t="n">
+      <c r="O44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P44" s="0" t="n">
+      <c r="P44" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C45" s="0" t="n">
+      <c r="C45" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="E45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G45" s="0" t="n">
+      <c r="G45" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="I45" s="0" t="n">
+      <c r="I45" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="J45" s="0" t="n">
+      <c r="J45" s="1" t="n">
         <v>415</v>
       </c>
-      <c r="K45" s="0" t="n">
+      <c r="K45" s="1" t="n">
         <v>415</v>
       </c>
-      <c r="L45" s="0" t="n">
+      <c r="L45" s="1" t="n">
         <v>5258.82</v>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="M45" s="2" t="n">
         <f aca="false">L45-(L45*0.1)</f>
         <v>4732.938</v>
       </c>
-      <c r="N45" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O45" s="0" t="n">
+      <c r="N45" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P45" s="0" t="n">
+      <c r="P45" s="1" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E46" s="0" t="s">
+      <c r="E46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G46" s="0" t="n">
+      <c r="G46" s="1" t="n">
         <v>595</v>
       </c>
-      <c r="H46" s="0" t="n">
+      <c r="H46" s="1" t="n">
         <v>580</v>
       </c>
-      <c r="I46" s="0" t="n">
+      <c r="I46" s="1" t="n">
         <v>1590</v>
       </c>
-      <c r="J46" s="0" t="n">
+      <c r="J46" s="1" t="n">
         <v>0.17</v>
       </c>
-      <c r="K46" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L46" s="0" t="n">
+      <c r="K46" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L46" s="1" t="n">
         <v>5258.82</v>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="M46" s="2" t="n">
         <f aca="false">L46-(L46*0.1)</f>
         <v>4732.938</v>
       </c>
-      <c r="N46" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O46" s="0" t="n">
+      <c r="N46" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P46" s="0" t="n">
+      <c r="P46" s="1" t="n">
         <v>115</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E47" s="0" t="s">
+      <c r="E47" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G47" s="0" t="n">
+      <c r="G47" s="1" t="n">
         <v>947</v>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="I47" s="0" t="n">
+      <c r="I47" s="1" t="n">
         <v>1342</v>
       </c>
-      <c r="J47" s="0" t="n">
+      <c r="J47" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="K47" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L47" s="0" t="n">
+      <c r="K47" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L47" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="M47" s="2" t="n">
         <f aca="false">L47-(L47*0.1)</f>
         <v>900</v>
       </c>
-      <c r="N47" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O47" s="0" t="n">
+      <c r="N47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O47" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="P47" s="0" t="n">
+      <c r="P47" s="1" t="n">
         <v>115</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G48" s="0" t="n">
+      <c r="G48" s="1" t="n">
         <v>409</v>
       </c>
-      <c r="H48" s="0" t="n">
+      <c r="H48" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="I48" s="0" t="n">
+      <c r="I48" s="1" t="n">
         <v>792</v>
       </c>
-      <c r="J48" s="0" t="n">
+      <c r="J48" s="1" t="n">
         <v>2.3</v>
       </c>
-      <c r="K48" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L48" s="0" t="n">
+      <c r="K48" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>7404.18</v>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="M48" s="2" t="n">
         <f aca="false">L48-(L48*0.1)</f>
         <v>6663.762</v>
       </c>
-      <c r="N48" s="0" t="s">
+      <c r="N48" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O48" s="0" t="n">
+      <c r="O48" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E49" s="0" t="s">
+      <c r="E49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G49" s="0" t="n">
+      <c r="G49" s="1" t="n">
         <v>585</v>
       </c>
-      <c r="H49" s="0" t="n">
+      <c r="H49" s="1" t="n">
         <v>304</v>
       </c>
-      <c r="I49" s="0" t="n">
+      <c r="I49" s="1" t="n">
         <v>304</v>
       </c>
-      <c r="J49" s="0" t="n">
+      <c r="J49" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K49" s="0" t="n">
+      <c r="K49" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L49" s="0" t="n">
+      <c r="L49" s="1" t="n">
         <v>2748.24</v>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="M49" s="2" t="n">
         <f aca="false">L49-(L49*0.1)</f>
         <v>2473.416</v>
       </c>
-      <c r="N49" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O49" s="0" t="n">
+      <c r="N49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O49" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="P49" s="0" t="n">
+      <c r="P49" s="1" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="E50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G50" s="0" t="n">
+      <c r="G50" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="I50" s="0" t="n">
+      <c r="I50" s="1" t="n">
         <v>455</v>
       </c>
-      <c r="J50" s="0" t="n">
+      <c r="J50" s="1" t="n">
         <v>415</v>
       </c>
-      <c r="K50" s="0" t="n">
+      <c r="K50" s="1" t="n">
         <v>415</v>
       </c>
-      <c r="L50" s="0" t="n">
+      <c r="L50" s="1" t="n">
         <v>140.7</v>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="M50" s="2" t="n">
         <f aca="false">L50-(L50*0.1)</f>
         <v>126.63</v>
       </c>
-      <c r="N50" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O50" s="0" t="n">
+      <c r="N50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O50" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="E51" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G51" s="0" t="n">
+      <c r="G51" s="1" t="n">
         <v>624</v>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51" s="1" t="n">
         <v>792</v>
       </c>
-      <c r="I51" s="0" t="n">
+      <c r="I51" s="1" t="n">
         <v>1367</v>
       </c>
-      <c r="J51" s="0" t="n">
+      <c r="J51" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="K51" s="0" t="n">
+      <c r="K51" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L51" s="0" t="n">
+      <c r="L51" s="1" t="n">
         <v>5589.42</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="M51" s="2" t="n">
         <f aca="false">L51-(L51*0.1)</f>
         <v>5030.478</v>
       </c>
-      <c r="N51" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O51" s="0" t="n">
+      <c r="N51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P51" s="0" t="n">
+      <c r="P51" s="1" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G52" s="0" t="n">
+      <c r="G52" s="1" t="n">
         <v>260</v>
       </c>
-      <c r="H52" s="0" t="n">
+      <c r="H52" s="1" t="n">
         <v>415</v>
       </c>
-      <c r="I52" s="0" t="n">
+      <c r="I52" s="1" t="n">
         <v>3.7</v>
       </c>
-      <c r="J52" s="0" t="n">
+      <c r="J52" s="1" t="n">
         <v>3.7</v>
       </c>
-      <c r="K52" s="0" t="n">
+      <c r="K52" s="1" t="n">
         <v>415</v>
       </c>
-      <c r="L52" s="0" t="n">
+      <c r="L52" s="1" t="n">
         <v>6658.56</v>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="M52" s="2" t="n">
         <f aca="false">L52-(L52*0.1)</f>
         <v>5992.704</v>
       </c>
-      <c r="N52" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O52" s="0" t="n">
+      <c r="N52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P52" s="0" t="n">
+      <c r="P52" s="1" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G53" s="0" t="n">
+      <c r="G53" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H53" s="0" t="n">
+      <c r="H53" s="1" t="n">
         <v>520</v>
       </c>
-      <c r="I53" s="0" t="n">
+      <c r="I53" s="1" t="n">
         <v>790</v>
       </c>
-      <c r="J53" s="0" t="n">
+      <c r="J53" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K53" s="0" t="n">
+      <c r="K53" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="L53" s="0" t="n">
+      <c r="L53" s="1" t="n">
         <v>863.22</v>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="M53" s="2" t="n">
         <f aca="false">L53-(L53*0.1)</f>
         <v>776.898</v>
       </c>
-      <c r="N53" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O53" s="0" t="n">
+      <c r="N53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="P53" s="0" t="n">
+      <c r="P53" s="1" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G54" s="0" t="n">
+      <c r="G54" s="1" t="n">
         <v>390</v>
       </c>
-      <c r="H54" s="0" t="n">
+      <c r="H54" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="I54" s="0" t="n">
+      <c r="I54" s="1" t="n">
         <v>275</v>
       </c>
-      <c r="J54" s="0" t="n">
+      <c r="J54" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K54" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L54" s="0" t="n">
+      <c r="K54" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L54" s="1" t="n">
         <v>240.96</v>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="M54" s="2" t="n">
         <f aca="false">L54-(L54*0.1)</f>
         <v>216.864</v>
       </c>
-      <c r="N54" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O54" s="0" t="n">
+      <c r="N54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O54" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="P54" s="0" t="n">
+      <c r="P54" s="1" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="E55" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="1" t="n">
         <v>490</v>
       </c>
-      <c r="I55" s="0" t="n">
+      <c r="I55" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="J55" s="0" t="n">
+      <c r="J55" s="1" t="n">
         <v>1.95</v>
       </c>
-      <c r="K55" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L55" s="0" t="n">
+      <c r="K55" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>205.62</v>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="M55" s="2" t="n">
         <f aca="false">L55-(L55*0.1)</f>
         <v>185.058</v>
       </c>
-      <c r="N55" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O55" s="0" t="n">
+      <c r="N55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P55" s="0" t="n">
+      <c r="P55" s="1" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="1" t="n">
         <v>101010</v>
       </c>
-      <c r="D56" s="0" t="n">
+      <c r="D56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="E56" s="0" t="s">
+      <c r="E56" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G56" s="0" t="n">
+      <c r="G56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I56" s="0" t="n">
+      <c r="I56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="J56" s="0" t="n">
+      <c r="J56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="K56" s="0" t="n">
+      <c r="K56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="L56" s="0" t="n">
+      <c r="L56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="M56" s="2" t="n">
         <f aca="false">L56-(L56*0.1)</f>
         <v>90</v>
       </c>
-      <c r="N56" s="0" t="s">
+      <c r="N56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O56" s="0" t="n">
+      <c r="O56" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="0" t="s">
+      <c r="C57" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E57" s="0" t="s">
+      <c r="E57" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G57" s="0" t="n">
+      <c r="G57" s="1" t="n">
         <v>410</v>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="I57" s="0" t="n">
+      <c r="I57" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="J57" s="0" t="n">
+      <c r="J57" s="1" t="n">
         <v>45414</v>
       </c>
-      <c r="K57" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L57" s="0" t="n">
+      <c r="K57" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L57" s="1" t="n">
         <v>26708.04</v>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="M57" s="2" t="n">
         <f aca="false">L57-(L57*0.1)</f>
         <v>24037.236</v>
       </c>
-      <c r="N57" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O57" s="0" t="n">
+      <c r="N57" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O57" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P57" s="0" t="n">
+      <c r="P57" s="1" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C58" s="0" t="s">
+      <c r="C58" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E58" s="0" t="s">
+      <c r="E58" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G58" s="0" t="n">
+      <c r="G58" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I58" s="0" t="n">
+      <c r="I58" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J58" s="0" t="n">
+      <c r="J58" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K58" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L58" s="0" t="n">
+      <c r="K58" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L58" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="M58" s="2" t="n">
         <f aca="false">L58-(L58*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N58" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O58" s="0" t="n">
+      <c r="N58" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O58" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P58" s="0" t="n">
+      <c r="P58" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C59" s="0" t="s">
+      <c r="C59" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E59" s="0" t="s">
+      <c r="E59" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G59" s="0" t="n">
+      <c r="G59" s="1" t="n">
         <v>4300</v>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="1" t="n">
         <v>3700</v>
       </c>
-      <c r="I59" s="0" t="n">
+      <c r="I59" s="1" t="n">
         <v>2100</v>
       </c>
-      <c r="J59" s="0" t="n">
+      <c r="J59" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K59" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L59" s="0" t="n">
+      <c r="K59" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L59" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="M59" s="2" t="n">
         <f aca="false">L59-(L59*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N59" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O59" s="0" t="n">
+      <c r="N59" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O59" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P59" s="0" t="n">
+      <c r="P59" s="1" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="C60" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E60" s="0" t="s">
+      <c r="E60" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G60" s="0" t="n">
+      <c r="G60" s="1" t="n">
         <v>497</v>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H60" s="1" t="n">
         <v>592</v>
       </c>
-      <c r="I60" s="0" t="n">
+      <c r="I60" s="1" t="n">
         <v>887</v>
       </c>
-      <c r="J60" s="0" t="n">
+      <c r="J60" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="K60" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L60" s="0" t="n">
+      <c r="K60" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L60" s="1" t="n">
         <v>151889.52</v>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="M60" s="2" t="n">
         <f aca="false">L60-(L60*0.1)</f>
         <v>136700.568</v>
       </c>
-      <c r="N60" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="P60" s="0" t="n">
+      <c r="N60" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P60" s="1" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C61" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E61" s="0" t="s">
+      <c r="E61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G61" s="0" t="n">
+      <c r="G61" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="I61" s="0" t="n">
+      <c r="I61" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J61" s="0" t="n">
+      <c r="J61" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="K61" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="L61" s="0" t="n">
+      <c r="K61" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L61" s="1" t="n">
         <v>22142.25</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="M61" s="2" t="n">
         <f aca="false">L61-(L61*0.1)</f>
         <v>19928.025</v>
       </c>
-      <c r="N61" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="O61" s="0" t="n">
+      <c r="N61" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O61" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="P61" s="0" t="n">
+      <c r="P61" s="1" t="n">
         <v>180</v>
       </c>
     </row>

--- a/TASKS/MP-251/test_import_file.xlsx
+++ b/TASKS/MP-251/test_import_file.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="191">
   <si>
     <t xml:space="preserve">Название</t>
   </si>
@@ -70,6 +70,27 @@
     <t xml:space="preserve">Сроки поставки</t>
   </si>
   <si>
+    <t xml:space="preserve">Изображения и файлы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парам_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парам_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парам_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парам_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парам_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парам_6</t>
+  </si>
+  <si>
     <t xml:space="preserve">РИСОВАРКА BECKERS</t>
   </si>
   <si>
@@ -89,6 +110,9 @@
   </si>
   <si>
     <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif</t>
   </si>
   <si>
     <t xml:space="preserve">ТЕРМОСТАТ ПОГРУЖНОЙ TATRA</t>
@@ -579,7 +603,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -600,6 +624,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -644,7 +675,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -654,6 +685,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -674,8 +709,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:W61"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="80.86"/>
   </cols>
@@ -729,25 +764,46 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>490</v>
@@ -772,27 +828,36 @@
         <v>178.974</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="U2" s="0" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>120</v>
@@ -817,30 +882,39 @@
         <v>31503.816</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="S3" s="0" t="n">
+        <v>222</v>
+      </c>
+      <c r="T3" s="0" t="n">
+        <v>222</v>
+      </c>
+      <c r="V3" s="0" t="n">
+        <v>222</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1835</v>
@@ -865,7 +939,7 @@
         <v>80646.327</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>45</v>
@@ -873,25 +947,34 @@
       <c r="P4" s="1" t="n">
         <v>135</v>
       </c>
+      <c r="Q4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="T4" s="0" t="n">
+        <v>333</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>180</v>
@@ -916,30 +999,36 @@
         <v>25648.218</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="T5" s="0" t="n">
+        <v>444</v>
+      </c>
+      <c r="U5" s="0" t="n">
+        <v>444</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>205</v>
@@ -964,10 +1053,19 @@
         <v>52.056</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>600</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <v>555</v>
+      </c>
+      <c r="V6" s="0" t="n">
+        <v>555</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -996,22 +1094,22 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1780</v>
@@ -1036,7 +1134,7 @@
         <v>4273.884</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>10</v>
@@ -1044,25 +1142,26 @@
       <c r="P11" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="Q11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1000</v>
@@ -1087,30 +1186,31 @@
         <v>900</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="Q12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>460</v>
@@ -1135,7 +1235,7 @@
         <v>7194.843</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>690</v>
@@ -1143,25 +1243,26 @@
       <c r="P13" s="1" t="n">
         <v>300</v>
       </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>430</v>
@@ -1186,7 +1287,7 @@
         <v>19928.025</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>77</v>
@@ -1194,25 +1295,26 @@
       <c r="P14" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>410</v>
@@ -1237,7 +1339,7 @@
         <v>24037.236</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>20</v>
@@ -1245,25 +1347,26 @@
       <c r="P15" s="1" t="n">
         <v>210</v>
       </c>
+      <c r="Q15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>430</v>
@@ -1288,7 +1391,7 @@
         <v>19928.025</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>77</v>
@@ -1296,25 +1399,29 @@
       <c r="P16" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q16" s="1"/>
+      <c r="W16" s="0" t="n">
+        <v>666</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>430</v>
@@ -1339,7 +1446,7 @@
         <v>19928.025</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>77</v>
@@ -1347,25 +1454,26 @@
       <c r="P17" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>490</v>
@@ -1390,27 +1498,27 @@
         <v>178.974</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>430</v>
@@ -1435,7 +1543,7 @@
         <v>19928.025</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>77</v>
@@ -1443,25 +1551,26 @@
       <c r="P19" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>120</v>
@@ -1486,7 +1595,7 @@
         <v>31503.816</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>6</v>
@@ -1494,22 +1603,22 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>1835</v>
@@ -1534,7 +1643,7 @@
         <v>80646.327</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>45</v>
@@ -1542,25 +1651,26 @@
       <c r="P21" s="1" t="n">
         <v>135</v>
       </c>
+      <c r="Q21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>180</v>
@@ -1585,7 +1695,7 @@
         <v>25648.218</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>2</v>
@@ -1593,22 +1703,22 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>205</v>
@@ -1633,7 +1743,7 @@
         <v>52.056</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>600</v>
@@ -1641,22 +1751,22 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>497</v>
@@ -1681,30 +1791,31 @@
         <v>136700.568</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>100</v>
       </c>
+      <c r="Q24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>535</v>
@@ -1729,27 +1840,27 @@
         <v>1561.95</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>697</v>
@@ -1774,30 +1885,31 @@
         <v>32281.83</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>132</v>
       </c>
+      <c r="Q26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>500</v>
@@ -1822,7 +1934,7 @@
         <v>505747.26</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>20</v>
@@ -1830,22 +1942,22 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>480</v>
@@ -1870,30 +1982,31 @@
         <v>28158.516</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="Q28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>1777</v>
@@ -1918,7 +2031,7 @@
         <v>72610.803</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>7</v>
@@ -1926,25 +2039,26 @@
       <c r="P29" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="Q29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>1300</v>
@@ -1969,27 +2083,27 @@
         <v>564750.225</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>800</v>
@@ -2014,7 +2128,7 @@
         <v>252510.003</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>1</v>
@@ -2022,25 +2136,26 @@
       <c r="P31" s="1" t="n">
         <v>115</v>
       </c>
+      <c r="Q31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1050</v>
@@ -2065,30 +2180,31 @@
         <v>43414.569</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>115</v>
       </c>
+      <c r="Q32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>19</v>
@@ -2113,27 +2229,27 @@
         <v>307.746</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>400</v>
@@ -2158,7 +2274,7 @@
         <v>169.182</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>100</v>
@@ -2166,22 +2282,22 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>460</v>
@@ -2206,7 +2322,7 @@
         <v>7194.843</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>690</v>
@@ -2214,25 +2330,26 @@
       <c r="P35" s="1" t="n">
         <v>300</v>
       </c>
+      <c r="Q35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>490</v>
@@ -2257,27 +2374,27 @@
         <v>178.974</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>430</v>
@@ -2302,7 +2419,7 @@
         <v>19928.025</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>77</v>
@@ -2310,25 +2427,26 @@
       <c r="P37" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>430</v>
@@ -2353,7 +2471,7 @@
         <v>19928.025</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>77</v>
@@ -2361,25 +2479,26 @@
       <c r="P38" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>111</v>
@@ -2404,7 +2523,7 @@
         <v>1110.6</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>11</v>
@@ -2412,25 +2531,26 @@
       <c r="P39" s="1" t="n">
         <v>111</v>
       </c>
+      <c r="Q39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>111</v>
@@ -2455,7 +2575,7 @@
         <v>1110.6</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>11</v>
@@ -2463,25 +2583,26 @@
       <c r="P40" s="1" t="n">
         <v>111</v>
       </c>
+      <c r="Q40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>497</v>
@@ -2506,30 +2627,31 @@
         <v>136700.568</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>100</v>
       </c>
+      <c r="Q41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>497</v>
@@ -2554,27 +2676,28 @@
         <v>136700.568</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P42" s="1" t="n">
         <v>100</v>
       </c>
+      <c r="Q42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>136021</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>600</v>
@@ -2599,27 +2722,27 @@
         <v>4732.938</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>1360</v>
@@ -2644,7 +2767,7 @@
         <v>4273.884</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>0</v>
@@ -2652,25 +2775,26 @@
       <c r="P44" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="Q44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>600</v>
@@ -2695,7 +2819,7 @@
         <v>4732.938</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>0</v>
@@ -2703,25 +2827,26 @@
       <c r="P45" s="1" t="n">
         <v>135</v>
       </c>
+      <c r="Q45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>595</v>
@@ -2746,7 +2871,7 @@
         <v>4732.938</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>20</v>
@@ -2754,25 +2879,26 @@
       <c r="P46" s="1" t="n">
         <v>115</v>
       </c>
+      <c r="Q46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>947</v>
@@ -2797,7 +2923,7 @@
         <v>900</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>15</v>
@@ -2805,25 +2931,26 @@
       <c r="P47" s="1" t="n">
         <v>115</v>
       </c>
+      <c r="Q47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>409</v>
@@ -2848,7 +2975,7 @@
         <v>6663.762</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>0</v>
@@ -2856,22 +2983,22 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>585</v>
@@ -2896,7 +3023,7 @@
         <v>2473.416</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>15</v>
@@ -2904,25 +3031,26 @@
       <c r="P49" s="1" t="n">
         <v>120</v>
       </c>
+      <c r="Q49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>155</v>
@@ -2947,7 +3075,7 @@
         <v>126.63</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>0</v>
@@ -2955,22 +3083,22 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>624</v>
@@ -2995,7 +3123,7 @@
         <v>5030.478</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>0</v>
@@ -3003,25 +3131,26 @@
       <c r="P51" s="1" t="n">
         <v>120</v>
       </c>
+      <c r="Q51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>260</v>
@@ -3046,7 +3175,7 @@
         <v>5992.704</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>0</v>
@@ -3054,25 +3183,26 @@
       <c r="P52" s="1" t="n">
         <v>120</v>
       </c>
+      <c r="Q52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>500</v>
@@ -3097,7 +3227,7 @@
         <v>776.898</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>15</v>
@@ -3105,25 +3235,26 @@
       <c r="P53" s="1" t="n">
         <v>120</v>
       </c>
+      <c r="Q53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>390</v>
@@ -3148,7 +3279,7 @@
         <v>216.864</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>15</v>
@@ -3156,25 +3287,26 @@
       <c r="P54" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="Q54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>490</v>
@@ -3199,7 +3331,7 @@
         <v>185.058</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>0</v>
@@ -3207,10 +3339,11 @@
       <c r="P55" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="Q55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B56" s="1" t="n">
         <v>1</v>
@@ -3222,10 +3355,10 @@
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>100</v>
@@ -3250,7 +3383,7 @@
         <v>90</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>0</v>
@@ -3258,22 +3391,22 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>410</v>
@@ -3298,7 +3431,7 @@
         <v>24037.236</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O57" s="1" t="n">
         <v>20</v>
@@ -3306,25 +3439,26 @@
       <c r="P57" s="1" t="n">
         <v>210</v>
       </c>
+      <c r="Q57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>430</v>
@@ -3349,7 +3483,7 @@
         <v>19928.025</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O58" s="1" t="n">
         <v>77</v>
@@ -3357,25 +3491,26 @@
       <c r="P58" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>4300</v>
@@ -3400,7 +3535,7 @@
         <v>19928.025</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O59" s="1" t="n">
         <v>77</v>
@@ -3408,25 +3543,26 @@
       <c r="P59" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>497</v>
@@ -3451,30 +3587,31 @@
         <v>136700.568</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>100</v>
       </c>
+      <c r="Q60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>430</v>
@@ -3499,7 +3636,7 @@
         <v>19928.025</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O61" s="1" t="n">
         <v>77</v>
@@ -3507,8 +3644,14 @@
       <c r="P61" s="1" t="n">
         <v>180</v>
       </c>
+      <c r="Q61" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q2" r:id="rId1" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="Q4" r:id="rId2" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="Q6" r:id="rId3" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/TASKS/MP-251/test_import_file.xlsx
+++ b/TASKS/MP-251/test_import_file.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="193">
   <si>
     <t xml:space="preserve">Название</t>
   </si>
@@ -70,6 +70,9 @@
     <t xml:space="preserve">Сроки поставки</t>
   </si>
   <si>
+    <t xml:space="preserve">файлы</t>
+  </si>
+  <si>
     <t xml:space="preserve">Изображения и файлы</t>
   </si>
   <si>
@@ -110,6 +113,9 @@
   </si>
   <si>
     <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://file1.jpg https://file2.png https://file3.jpeg https://file4.gif</t>
   </si>
   <si>
     <t xml:space="preserve">https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif</t>
@@ -603,7 +609,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -631,6 +637,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -675,7 +687,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -689,6 +701,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -709,8 +725,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:X61"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="80.86"/>
   </cols>
@@ -785,25 +801,28 @@
       <c r="W1" s="0" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="0" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>490</v>
@@ -828,36 +847,39 @@
         <v>178.974</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="0" t="n">
         <v>111</v>
       </c>
-      <c r="U2" s="0" t="n">
+      <c r="V2" s="0" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>120</v>
@@ -882,39 +904,39 @@
         <v>31503.816</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="S3" s="0" t="n">
-        <v>222</v>
-      </c>
       <c r="T3" s="0" t="n">
         <v>222</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="U3" s="0" t="n">
+        <v>222</v>
+      </c>
+      <c r="W3" s="0" t="n">
         <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1835</v>
@@ -939,7 +961,7 @@
         <v>80646.327</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>45</v>
@@ -947,34 +969,37 @@
       <c r="P4" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="Q4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" s="0" t="n">
-        <v>333</v>
+      <c r="Q4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="T4" s="0" t="n">
         <v>333</v>
       </c>
+      <c r="U4" s="0" t="n">
+        <v>333</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>180</v>
@@ -999,36 +1024,36 @@
         <v>25648.218</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="T5" s="0" t="n">
-        <v>444</v>
-      </c>
       <c r="U5" s="0" t="n">
         <v>444</v>
       </c>
+      <c r="V5" s="0" t="n">
+        <v>444</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>205</v>
@@ -1053,18 +1078,21 @@
         <v>52.056</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>600</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R6" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" s="0" t="n">
         <v>555</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="W6" s="0" t="n">
         <v>555</v>
       </c>
     </row>
@@ -1094,22 +1122,22 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1780</v>
@@ -1134,7 +1162,7 @@
         <v>4273.884</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>10</v>
@@ -1143,25 +1171,26 @@
         <v>2</v>
       </c>
       <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1000</v>
@@ -1186,31 +1215,32 @@
         <v>900</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>460</v>
@@ -1235,7 +1265,7 @@
         <v>7194.843</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>690</v>
@@ -1244,25 +1274,26 @@
         <v>300</v>
       </c>
       <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>430</v>
@@ -1287,7 +1318,7 @@
         <v>19928.025</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>77</v>
@@ -1296,25 +1327,26 @@
         <v>180</v>
       </c>
       <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>410</v>
@@ -1339,7 +1371,7 @@
         <v>24037.236</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>20</v>
@@ -1348,25 +1380,26 @@
         <v>210</v>
       </c>
       <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>430</v>
@@ -1391,7 +1424,7 @@
         <v>19928.025</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>77</v>
@@ -1400,28 +1433,29 @@
         <v>180</v>
       </c>
       <c r="Q16" s="1"/>
-      <c r="W16" s="0" t="n">
+      <c r="R16" s="1"/>
+      <c r="X16" s="0" t="n">
         <v>666</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>430</v>
@@ -1446,7 +1480,7 @@
         <v>19928.025</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>77</v>
@@ -1455,25 +1489,26 @@
         <v>180</v>
       </c>
       <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>490</v>
@@ -1498,27 +1533,27 @@
         <v>178.974</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>430</v>
@@ -1543,7 +1578,7 @@
         <v>19928.025</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>77</v>
@@ -1552,25 +1587,26 @@
         <v>180</v>
       </c>
       <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>120</v>
@@ -1595,7 +1631,7 @@
         <v>31503.816</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>6</v>
@@ -1603,22 +1639,22 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>1835</v>
@@ -1643,7 +1679,7 @@
         <v>80646.327</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>45</v>
@@ -1652,25 +1688,26 @@
         <v>135</v>
       </c>
       <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>180</v>
@@ -1695,7 +1732,7 @@
         <v>25648.218</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>2</v>
@@ -1703,22 +1740,22 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>205</v>
@@ -1743,7 +1780,7 @@
         <v>52.056</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>600</v>
@@ -1751,22 +1788,22 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>497</v>
@@ -1791,31 +1828,32 @@
         <v>136700.568</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>100</v>
       </c>
       <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>535</v>
@@ -1840,27 +1878,27 @@
         <v>1561.95</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>697</v>
@@ -1885,31 +1923,32 @@
         <v>32281.83</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>132</v>
       </c>
       <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>500</v>
@@ -1934,7 +1973,7 @@
         <v>505747.26</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>20</v>
@@ -1942,22 +1981,22 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>480</v>
@@ -1982,31 +2021,32 @@
         <v>28158.516</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>67</v>
       </c>
       <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>1777</v>
@@ -2031,7 +2071,7 @@
         <v>72610.803</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>7</v>
@@ -2040,25 +2080,26 @@
         <v>77</v>
       </c>
       <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>1300</v>
@@ -2083,27 +2124,27 @@
         <v>564750.225</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>800</v>
@@ -2128,7 +2169,7 @@
         <v>252510.003</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>1</v>
@@ -2137,25 +2178,26 @@
         <v>115</v>
       </c>
       <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1050</v>
@@ -2180,31 +2222,32 @@
         <v>43414.569</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>115</v>
       </c>
       <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>19</v>
@@ -2229,27 +2272,27 @@
         <v>307.746</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>400</v>
@@ -2274,7 +2317,7 @@
         <v>169.182</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>100</v>
@@ -2282,22 +2325,22 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>460</v>
@@ -2322,7 +2365,7 @@
         <v>7194.843</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>690</v>
@@ -2331,25 +2374,26 @@
         <v>300</v>
       </c>
       <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>490</v>
@@ -2374,27 +2418,27 @@
         <v>178.974</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>430</v>
@@ -2419,7 +2463,7 @@
         <v>19928.025</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>77</v>
@@ -2428,25 +2472,26 @@
         <v>180</v>
       </c>
       <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>430</v>
@@ -2471,7 +2516,7 @@
         <v>19928.025</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>77</v>
@@ -2480,25 +2525,26 @@
         <v>180</v>
       </c>
       <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>111</v>
@@ -2523,7 +2569,7 @@
         <v>1110.6</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>11</v>
@@ -2532,25 +2578,26 @@
         <v>111</v>
       </c>
       <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>111</v>
@@ -2575,7 +2622,7 @@
         <v>1110.6</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>11</v>
@@ -2584,25 +2631,26 @@
         <v>111</v>
       </c>
       <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>497</v>
@@ -2627,31 +2675,32 @@
         <v>136700.568</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>100</v>
       </c>
       <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>497</v>
@@ -2676,28 +2725,29 @@
         <v>136700.568</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P42" s="1" t="n">
         <v>100</v>
       </c>
       <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>136021</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>600</v>
@@ -2722,27 +2772,27 @@
         <v>4732.938</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>1360</v>
@@ -2767,7 +2817,7 @@
         <v>4273.884</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>0</v>
@@ -2776,25 +2826,26 @@
         <v>2</v>
       </c>
       <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>600</v>
@@ -2819,7 +2870,7 @@
         <v>4732.938</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>0</v>
@@ -2828,25 +2879,26 @@
         <v>135</v>
       </c>
       <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>595</v>
@@ -2871,7 +2923,7 @@
         <v>4732.938</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>20</v>
@@ -2880,25 +2932,26 @@
         <v>115</v>
       </c>
       <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>947</v>
@@ -2923,7 +2976,7 @@
         <v>900</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>15</v>
@@ -2932,25 +2985,26 @@
         <v>115</v>
       </c>
       <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>409</v>
@@ -2975,7 +3029,7 @@
         <v>6663.762</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>0</v>
@@ -2983,22 +3037,22 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>585</v>
@@ -3023,7 +3077,7 @@
         <v>2473.416</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>15</v>
@@ -3032,25 +3086,26 @@
         <v>120</v>
       </c>
       <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>155</v>
@@ -3075,7 +3130,7 @@
         <v>126.63</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>0</v>
@@ -3083,22 +3138,22 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>624</v>
@@ -3123,7 +3178,7 @@
         <v>5030.478</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>0</v>
@@ -3132,25 +3187,26 @@
         <v>120</v>
       </c>
       <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>260</v>
@@ -3175,7 +3231,7 @@
         <v>5992.704</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>0</v>
@@ -3184,25 +3240,26 @@
         <v>120</v>
       </c>
       <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>500</v>
@@ -3227,7 +3284,7 @@
         <v>776.898</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>15</v>
@@ -3236,25 +3293,26 @@
         <v>120</v>
       </c>
       <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>390</v>
@@ -3279,7 +3337,7 @@
         <v>216.864</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>15</v>
@@ -3288,25 +3346,26 @@
         <v>90</v>
       </c>
       <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>490</v>
@@ -3331,7 +3390,7 @@
         <v>185.058</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>0</v>
@@ -3340,10 +3399,11 @@
         <v>90</v>
       </c>
       <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B56" s="1" t="n">
         <v>1</v>
@@ -3355,10 +3415,10 @@
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>100</v>
@@ -3383,7 +3443,7 @@
         <v>90</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>0</v>
@@ -3391,22 +3451,22 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>410</v>
@@ -3431,7 +3491,7 @@
         <v>24037.236</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O57" s="1" t="n">
         <v>20</v>
@@ -3440,25 +3500,26 @@
         <v>210</v>
       </c>
       <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>430</v>
@@ -3483,7 +3544,7 @@
         <v>19928.025</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O58" s="1" t="n">
         <v>77</v>
@@ -3492,25 +3553,26 @@
         <v>180</v>
       </c>
       <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E59" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>4300</v>
@@ -3535,7 +3597,7 @@
         <v>19928.025</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O59" s="1" t="n">
         <v>77</v>
@@ -3544,25 +3606,26 @@
         <v>180</v>
       </c>
       <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>497</v>
@@ -3587,31 +3650,32 @@
         <v>136700.568</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>100</v>
       </c>
       <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>430</v>
@@ -3636,7 +3700,7 @@
         <v>19928.025</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O61" s="1" t="n">
         <v>77</v>
@@ -3645,12 +3709,16 @@
         <v>180</v>
       </c>
       <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
-    <hyperlink ref="Q4" r:id="rId2" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
-    <hyperlink ref="Q6" r:id="rId3" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="Q2" r:id="rId1" display="https://file4"/>
+    <hyperlink ref="R2" r:id="rId2" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="Q4" r:id="rId3" display="https://file4"/>
+    <hyperlink ref="R4" r:id="rId4" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="Q6" r:id="rId5" display="https://file4.gif"/>
+    <hyperlink ref="R6" r:id="rId6" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/TASKS/MP-251/test_import_file.xlsx
+++ b/TASKS/MP-251/test_import_file.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="203">
   <si>
     <t xml:space="preserve">Название</t>
   </si>
@@ -94,154 +94,184 @@
     <t xml:space="preserve">Парам_6</t>
   </si>
   <si>
+    <t xml:space="preserve">характеристика1 (Вт)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">характеристика2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">доп.фото</t>
+  </si>
+  <si>
+    <t xml:space="preserve">характеристика3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Блендер BECKERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">490*490*350 мм, 220В, 1.95 кВт, 9 кг, температура max +160°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-RIS8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beckers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/БЛЕНДЕРЫ БАРНЫЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Япония</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://filestorage.com/123/document.pdf https://filestorage.com/123/instruction.doc https://file3.jpeg https://file4.gif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://imgur.com/123/картинка2.png https://imgur.com/123/картинка3.png https://picture3.jpeg https://picture4.gif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 мм.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://imgur.com/123/instruction.jpg https://imgur.com/123/картинка3.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://imgur.com/123/картинка2.png https://filestorage.com/123/instruction.doc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТЕРМОСТАТ ПОГРУЖНОЙ TATRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Погружной термостат TSV2 предназначен для приготовления широкого спектра блюд по технологии Sous Vide.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-TSV2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Румыния</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТОЛ С ОХЛАЖД.ШКАФОМ HICOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Регулируемые по высоте ножки, автоматические доводчики дверей с фиксатором открытого положения, легкозаменяемые магнитные уплотнители</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-GN111/TN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://file1.jpg https://file2.png https://file3.jpeg https://file4.gif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЛЕНДЕР BORK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180х220х440 мм, 220 В, 1,3 кВт, блендер, 5 скоростей - до 12000 об./мин., создавайте насыщенный густой смузи с функцией Smoothie, а в режиме Ice Crush - идеальную ледяную крошку.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-B705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЛЕНДЕР HURAKAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205x230x510, 220 В, 1,2 кВт, 3.5кг, 23000-26000 об/мин, режим пульсации, объём стакана 2 л, материал стакана пластик, материал корпуса пластик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-HKN-BLW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШКАФ РАССТОЕЧНЫЙ SOTTORIVA MODUL 3 CEL 3-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1780x1035x845 мм, 180 кг, 1кВт, 380В, на колесиках, для печей MODUL 3 с 1-2 камерами (уровнями). Регулировка температуры и вентиляции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sottoriva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ХОЛОДИЛЬНОЕ ОБОРУДОВАНИЕ/ШКАФЫ ВИННЫЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Казахстан</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коробка-стелаж винная</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крутая тестовая коробка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РИСОВАРКА HURAKAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рисоварка Hurakan – отличное решение для приготовления риса в суши-барах, в ресторанах японской и китайской кухни, столовых и везде, где требуется готовить большое количество риса.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HKN-SR56M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HURAKAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Китай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГРИЛЬ КОНТАКТНЫЙ HURAKAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контактные грили Hurakan – универсальное оборудование для профессиональной кухни.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HKN-PE34R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Алжир</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГРИЛЬ КОНТАКТНЫЙ TATRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контактный гриль TATRA TCG 3627 RR предназначен для использования на предприятиях общественного питания и торговли для разогрева блюд из мяса, птицы и овощей, а также приготовления горячих бутербродов и сэндвичей.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCG 3627 RR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПОСУДА И ИНВЕНТАРЬ/ФАРФОР, КЕРАМИКА/04.01.06. PORDAMSA/04.01.06.20. CASUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аландские острова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/АКСЕССУАРЫ ДЛЯ БАРНОГО ОБОРУДОВАНИЯ/ДИСПЕНСЕРЫ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HKN-PE34Rк</t>
+  </si>
+  <si>
     <t xml:space="preserve">РИСОВАРКА BECKERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">490*490*350 мм, 220В, 1.95 кВт, 9 кг, температура max +160°C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-RIS8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beckers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/БЛЕНДЕРЫ БАРНЫЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Япония</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://file1.jpg https://file2.png https://file3.jpeg https://file4.gif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТЕРМОСТАТ ПОГРУЖНОЙ TATRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Погружной термостат TSV2 предназначен для приготовления широкого спектра блюд по технологии Sous Vide.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-TSV2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Румыния</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СТОЛ С ОХЛАЖД.ШКАФОМ HICOLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Регулируемые по высоте ножки, автоматические доводчики дверей с фиксатором открытого положения, легкозаменяемые магнитные уплотнители</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-GN111/TN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЛЕНДЕР BORK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180х220х440 мм, 220 В, 1,3 кВт, блендер, 5 скоростей - до 12000 об./мин., создавайте насыщенный густой смузи с функцией Smoothie, а в режиме Ice Crush - идеальную ледяную крошку.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-B705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЛЕНДЕР HURAKAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205x230x510, 220 В, 1,2 кВт, 3.5кг, 23000-26000 об/мин, режим пульсации, объём стакана 2 л, материал стакана пластик, материал корпуса пластик</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-HKN-BLW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ШКАФ РАССТОЕЧНЫЙ SOTTORIVA MODUL 3 CEL 3-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1780x1035x845 мм, 180 кг, 1кВт, 380В, на колесиках, для печей MODUL 3 с 1-2 камерами (уровнями). Регулировка температуры и вентиляции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sottoriva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ХОЛОДИЛЬНОЕ ОБОРУДОВАНИЕ/ШКАФЫ ВИННЫЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Казахстан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Коробка-стелаж винная</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Крутая тестовая коробка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РИСОВАРКА HURAKAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рисоварка Hurakan – отличное решение для приготовления риса в суши-барах, в ресторанах японской и китайской кухни, столовых и везде, где требуется готовить большое количество риса.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HKN-SR56M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HURAKAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Китай</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ГРИЛЬ КОНТАКТНЫЙ HURAKAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Контактные грили Hurakan – универсальное оборудование для профессиональной кухни.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HKN-PE34R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Алжир</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ГРИЛЬ КОНТАКТНЫЙ TATRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Контактный гриль TATRA TCG 3627 RR предназначен для использования на предприятиях общественного питания и торговли для разогрева блюд из мяса, птицы и овощей, а также приготовления горячих бутербродов и сэндвичей.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCG 3627 RR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TATRA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПОСУДА И ИНВЕНТАРЬ/ФАРФОР, КЕРАМИКА/04.01.06. PORDAMSA/04.01.06.20. CASUAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аландские острова</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БАРНОЕ ОБОРУДОВАНИЕ/АКСЕССУАРЫ ДЛЯ БАРНОГО ОБОРУДОВАНИЯ/ДИСПЕНСЕРЫ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HKN-PE34Rк</t>
   </si>
   <si>
     <t xml:space="preserve">RIS8</t>
@@ -609,7 +639,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -637,12 +667,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -696,15 +720,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -725,13 +749,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB57"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="80.86"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,25 +828,37 @@
       <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>490</v>
@@ -842,18 +878,18 @@
       <c r="L2" s="1" t="n">
         <v>198.86</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="3" t="n">
         <f aca="false">L2-(L2*0.1)</f>
         <v>178.974</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="S2" s="0" t="n">
         <v>111</v>
@@ -861,25 +897,37 @@
       <c r="V2" s="0" t="n">
         <v>111</v>
       </c>
+      <c r="Y2" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>120</v>
@@ -899,12 +947,12 @@
       <c r="L3" s="1" t="n">
         <v>35004.24</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="3" t="n">
         <f aca="false">L3-(L3*0.1)</f>
         <v>31503.816</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>6</v>
@@ -921,22 +969,22 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1835</v>
@@ -956,12 +1004,12 @@
       <c r="L4" s="1" t="n">
         <v>89607.03</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="3" t="n">
         <f aca="false">L4-(L4*0.1)</f>
         <v>80646.327</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>45</v>
@@ -970,10 +1018,10 @@
         <v>135</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>32</v>
+        <v>49</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="T4" s="0" t="n">
         <v>333</v>
@@ -984,22 +1032,22 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>180</v>
@@ -1019,12 +1067,12 @@
       <c r="L5" s="1" t="n">
         <v>28498.02</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="3" t="n">
         <f aca="false">L5-(L5*0.1)</f>
         <v>25648.218</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>2</v>
@@ -1038,22 +1086,22 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>205</v>
@@ -1073,21 +1121,21 @@
       <c r="L6" s="1" t="n">
         <v>57.84</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="3" t="n">
         <f aca="false">L6-(L6*0.1)</f>
         <v>52.056</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="Q6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>32</v>
+      <c r="Q6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="S6" s="0" t="n">
         <v>555</v>
@@ -1097,1987 +1145,2170 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M7" s="2" t="n">
+      <c r="A7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1780</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1035</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>845</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>4748.76</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <f aca="false">L7-(L7*0.1)</f>
-        <v>0</v>
-      </c>
+        <v>4273.884</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M8" s="2" t="n">
+      <c r="A8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <f aca="false">L8-(L8*0.1)</f>
-        <v>0</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M9" s="2" t="n">
+      <c r="A9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>460</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>460</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>375</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>7994.27</v>
+      </c>
+      <c r="M9" s="3" t="n">
         <f aca="false">L9-(L9*0.1)</f>
-        <v>0</v>
-      </c>
+        <v>7194.843</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>690</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M10" s="2" t="n">
+      <c r="A10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>430</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>370</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M10" s="3" t="n">
         <f aca="false">L10-(L10*0.1)</f>
-        <v>0</v>
-      </c>
+        <v>19928.025</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1780</v>
+        <v>410</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1035</v>
+        <v>500</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>845</v>
+        <v>300</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>1</v>
+        <v>45414</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>4748.76</v>
-      </c>
-      <c r="M11" s="2" t="n">
+        <v>26708.04</v>
+      </c>
+      <c r="M11" s="3" t="n">
         <f aca="false">L11-(L11*0.1)</f>
-        <v>4273.884</v>
+        <v>24037.236</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>14</v>
+        <v>72</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="2" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <f aca="false">L12-(L12*0.1)</f>
-        <v>900</v>
+        <v>19928.025</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>77</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
+      <c r="X12" s="0" t="n">
+        <v>666</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>375</v>
+        <v>210</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>7994.27</v>
-      </c>
-      <c r="M13" s="2" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M13" s="3" t="n">
         <f aca="false">L13-(L13*0.1)</f>
-        <v>7194.843</v>
+        <v>19928.025</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>690</v>
+        <v>77</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>370</v>
+        <v>490</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M14" s="2" t="n">
+        <v>198.86</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <f aca="false">L14-(L14*0.1)</f>
-        <v>19928.025</v>
+        <v>178.974</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>45414</v>
+        <v>2.2</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>26708.04</v>
-      </c>
-      <c r="M15" s="2" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <f aca="false">L15-(L15*0.1)</f>
-        <v>24037.236</v>
+        <v>19928.025</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>430</v>
+        <v>120</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>370</v>
+        <v>145</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M16" s="2" t="n">
+        <v>35004.24</v>
+      </c>
+      <c r="M16" s="3" t="n">
         <f aca="false">L16-(L16*0.1)</f>
-        <v>19928.025</v>
+        <v>31503.816</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="X16" s="0" t="n">
-        <v>666</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>430</v>
+        <v>1835</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>210</v>
+        <v>850</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>2.2</v>
+        <v>0.46</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M17" s="2" t="n">
+        <v>89607.03</v>
+      </c>
+      <c r="M17" s="3" t="n">
         <f aca="false">L17-(L17*0.1)</f>
-        <v>19928.025</v>
+        <v>80646.327</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G18" s="1" t="n">
-        <v>490</v>
+        <v>180</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>490</v>
+        <v>220</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>198.86</v>
-      </c>
-      <c r="M18" s="2" t="n">
+        <v>28498.02</v>
+      </c>
+      <c r="M18" s="3" t="n">
         <f aca="false">L18-(L18*0.1)</f>
-        <v>178.974</v>
+        <v>25648.218</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>430</v>
+        <v>205</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>370</v>
+        <v>230</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M19" s="2" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <f aca="false">L19-(L19*0.1)</f>
-        <v>19928.025</v>
+        <v>52.056</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
+        <v>600</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>120</v>
+        <v>497</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>145</v>
+        <v>592</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>340</v>
+        <v>887</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>35004.24</v>
-      </c>
-      <c r="M20" s="2" t="n">
+        <v>151889.52</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <f aca="false">L20-(L20*0.1)</f>
-        <v>31503.816</v>
+        <v>136700.568</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>6</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>1835</v>
+        <v>535</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>850</v>
+        <v>910</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.46</v>
+        <v>0.69</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>89607.03</v>
-      </c>
-      <c r="M21" s="2" t="n">
+        <v>1735.5</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <f aca="false">L21-(L21*0.1)</f>
-        <v>80646.327</v>
+        <v>1561.95</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>180</v>
+        <v>697</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>220</v>
+        <v>710</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>440</v>
+        <v>1960</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1.3</v>
+        <v>0.35</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>28498.02</v>
-      </c>
-      <c r="M22" s="2" t="n">
+        <v>35868.7</v>
+      </c>
+      <c r="M22" s="3" t="n">
         <f aca="false">L22-(L22*0.1)</f>
-        <v>25648.218</v>
+        <v>32281.83</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>2</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>205</v>
+        <v>500</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>230</v>
+        <v>610</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>510</v>
+        <v>630</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>57.84</v>
-      </c>
-      <c r="M23" s="2" t="n">
+        <v>561941.4</v>
+      </c>
+      <c r="M23" s="3" t="n">
         <f aca="false">L23-(L23*0.1)</f>
-        <v>52.056</v>
+        <v>505747.26</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>600</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="G24" s="1" t="n">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>592</v>
+        <v>560</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>887</v>
+        <v>1000</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>151889.52</v>
-      </c>
-      <c r="M24" s="2" t="n">
+        <v>31287.24</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <f aca="false">L24-(L24*0.1)</f>
-        <v>136700.568</v>
+        <v>28158.516</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>535</v>
+        <v>1777</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>910</v>
+        <v>850</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.69</v>
+        <v>0.2</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>1735.5</v>
-      </c>
-      <c r="M25" s="2" t="n">
+        <v>80678.67</v>
+      </c>
+      <c r="M25" s="3" t="n">
         <f aca="false">L25-(L25*0.1)</f>
-        <v>1561.95</v>
+        <v>72610.803</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>697</v>
+        <v>1300</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>1960</v>
+        <v>950</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>35868.7</v>
-      </c>
-      <c r="M26" s="2" t="n">
+        <v>627500.25</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <f aca="false">L26-(L26*0.1)</f>
-        <v>32281.83</v>
+        <v>564750.225</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>610</v>
+        <v>840</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>630</v>
+        <v>1055</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>380</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>561941.4</v>
-      </c>
-      <c r="M27" s="2" t="n">
+        <v>280566.67</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <f aca="false">L27-(L27*0.1)</f>
-        <v>505747.26</v>
+        <v>252510.003</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>20</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>480</v>
+        <v>1050</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>560</v>
+        <v>895</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>1000</v>
+        <v>860</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>3.6</v>
+        <v>16.8</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>31287.24</v>
-      </c>
-      <c r="M28" s="2" t="n">
+        <v>48238.41</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <f aca="false">L28-(L28*0.1)</f>
-        <v>28158.516</v>
+        <v>43414.569</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>1777</v>
+        <v>19</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>700</v>
+        <v>216</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.2</v>
+        <v>1.19</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>80678.67</v>
-      </c>
-      <c r="M29" s="2" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="M29" s="3" t="n">
         <f aca="false">L29-(L29*0.1)</f>
-        <v>72610.803</v>
+        <v>307.746</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>700</v>
+        <v>310</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>950</v>
+        <v>420</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>627500.25</v>
-      </c>
-      <c r="M30" s="2" t="n">
+        <v>187.98</v>
+      </c>
+      <c r="M30" s="3" t="n">
         <f aca="false">L30-(L30*0.1)</f>
-        <v>564750.225</v>
+        <v>169.182</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>800</v>
+        <v>460</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>840</v>
+        <v>460</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>1055</v>
+        <v>375</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>280566.67</v>
-      </c>
-      <c r="M31" s="2" t="n">
+        <v>7994.27</v>
+      </c>
+      <c r="M31" s="3" t="n">
         <f aca="false">L31-(L31*0.1)</f>
-        <v>252510.003</v>
+        <v>7194.843</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>1</v>
+        <v>690</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>1050</v>
+        <v>490</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>895</v>
+        <v>490</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>860</v>
+        <v>340</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>16.8</v>
+        <v>1.99</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>48238.41</v>
-      </c>
-      <c r="M32" s="2" t="n">
+        <v>198.86</v>
+      </c>
+      <c r="M32" s="3" t="n">
         <f aca="false">L32-(L32*0.1)</f>
-        <v>43414.569</v>
+        <v>178.974</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P32" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>19</v>
+        <v>430</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>216</v>
+        <v>370</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>400</v>
+        <v>210</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>1.19</v>
+        <v>2.2</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>341.94</v>
-      </c>
-      <c r="M33" s="2" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M33" s="3" t="n">
         <f aca="false">L33-(L33*0.1)</f>
-        <v>307.746</v>
+        <v>19928.025</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.15</v>
+        <v>2.2</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>187.98</v>
-      </c>
-      <c r="M34" s="2" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M34" s="3" t="n">
         <f aca="false">L34-(L34*0.1)</f>
-        <v>169.182</v>
+        <v>19928.025</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>100</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>61</v>
+        <v>154</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>460</v>
+        <v>111</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>460</v>
+        <v>111</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>375</v>
+        <v>111</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>7994.27</v>
-      </c>
-      <c r="M35" s="2" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M35" s="3" t="n">
         <f aca="false">L35-(L35*0.1)</f>
-        <v>7194.843</v>
+        <v>1110.6</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>690</v>
+        <v>11</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>300</v>
+        <v>111</v>
       </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>490</v>
+        <v>111</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>490</v>
+        <v>111</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>340</v>
+        <v>111</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>1.99</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>198.86</v>
-      </c>
-      <c r="M36" s="2" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M36" s="3" t="n">
         <f aca="false">L36-(L36*0.1)</f>
-        <v>178.974</v>
+        <v>1110.6</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>430</v>
+        <v>497</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>370</v>
+        <v>592</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>210</v>
+        <v>887</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M37" s="2" t="n">
+        <v>151889.52</v>
+      </c>
+      <c r="M37" s="3" t="n">
         <f aca="false">L37-(L37*0.1)</f>
-        <v>19928.025</v>
+        <v>136700.568</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O37" s="1" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>430</v>
+        <v>497</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>370</v>
+        <v>592</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>210</v>
+        <v>887</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M38" s="2" t="n">
+        <v>151889.52</v>
+      </c>
+      <c r="M38" s="3" t="n">
         <f aca="false">L38-(L38*0.1)</f>
-        <v>19928.025</v>
+        <v>136700.568</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O38" s="1" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>141</v>
+        <v>164</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>136021</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>111</v>
+        <v>600</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>111</v>
+        <v>600</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>111</v>
+        <v>600</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1234</v>
-      </c>
-      <c r="M39" s="2" t="n">
+        <v>5258.82</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <f aca="false">L39-(L39*0.1)</f>
-        <v>1110.6</v>
+        <v>4732.938</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O39" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="P39" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>143</v>
+        <v>32</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>111</v>
+        <v>1360</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>111</v>
+        <v>1760</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>111</v>
+        <v>1750</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1234</v>
-      </c>
-      <c r="M40" s="2" t="n">
+        <v>4748.76</v>
+      </c>
+      <c r="M40" s="3" t="n">
         <f aca="false">L40-(L40*0.1)</f>
-        <v>1110.6</v>
+        <v>4273.884</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>150</v>
+        <v>168</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>497</v>
+        <v>600</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>592</v>
+        <v>400</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>887</v>
+        <v>20</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.6</v>
+        <v>415</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>220</v>
+        <v>415</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>151889.52</v>
-      </c>
-      <c r="M41" s="2" t="n">
+        <v>5258.82</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <f aca="false">L41-(L41*0.1)</f>
-        <v>136700.568</v>
+        <v>4732.938</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="O41" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>152</v>
+        <v>170</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>497</v>
+        <v>595</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>887</v>
+        <v>1590</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>151889.52</v>
-      </c>
-      <c r="M42" s="2" t="n">
+        <v>5258.82</v>
+      </c>
+      <c r="M42" s="3" t="n">
         <f aca="false">L42-(L42*0.1)</f>
-        <v>136700.568</v>
+        <v>4732.938</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="O42" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>136021</v>
+        <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>51</v>
+        <v>171</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>155</v>
+        <v>79</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>600</v>
+        <v>947</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>600</v>
+        <v>1342</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>600</v>
+        <v>0.3</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>5258.82</v>
-      </c>
-      <c r="M43" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M43" s="3" t="n">
         <f aca="false">L43-(L43*0.1)</f>
-        <v>4732.938</v>
+        <v>900</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="O43" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>1360</v>
+        <v>409</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>1760</v>
+        <v>38</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>1750</v>
+        <v>792</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>4748.76</v>
-      </c>
-      <c r="M44" s="2" t="n">
+        <v>7404.18</v>
+      </c>
+      <c r="M44" s="3" t="n">
         <f aca="false">L44-(L44*0.1)</f>
-        <v>4273.884</v>
+        <v>6663.762</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P44" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C45" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>585</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="J45" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>600</v>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>400</v>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J45" s="1" t="n">
-        <v>415</v>
-      </c>
       <c r="K45" s="1" t="n">
-        <v>415</v>
+        <v>380</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>5258.82</v>
-      </c>
-      <c r="M45" s="2" t="n">
+        <v>2748.24</v>
+      </c>
+      <c r="M45" s="3" t="n">
         <f aca="false">L45-(L45*0.1)</f>
-        <v>4732.938</v>
+        <v>2473.416</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>595</v>
+        <v>155</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>580</v>
+        <v>155</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>1590</v>
+        <v>455</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>0.17</v>
+        <v>415</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>220</v>
+        <v>415</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>5258.82</v>
-      </c>
-      <c r="M46" s="2" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="M46" s="3" t="n">
         <f aca="false">L46-(L46*0.1)</f>
-        <v>4732.938</v>
+        <v>126.63</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>947</v>
+        <v>624</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>720</v>
+        <v>792</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>1342</v>
+        <v>1367</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M47" s="2" t="n">
+        <v>5589.42</v>
+      </c>
+      <c r="M47" s="3" t="n">
         <f aca="false">L47-(L47*0.1)</f>
-        <v>900</v>
+        <v>5030.478</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>409</v>
+        <v>260</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>38</v>
+        <v>415</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>792</v>
+        <v>3.7</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>220</v>
+        <v>415</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>7404.18</v>
-      </c>
-      <c r="M48" s="2" t="n">
+        <v>6658.56</v>
+      </c>
+      <c r="M48" s="3" t="n">
         <f aca="false">L48-(L48*0.1)</f>
-        <v>6663.762</v>
+        <v>5992.704</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="P48" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>166</v>
+        <v>31</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>585</v>
+        <v>500</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>304</v>
+        <v>520</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>304</v>
+        <v>790</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>2748.24</v>
-      </c>
-      <c r="M49" s="2" t="n">
+        <v>863.22</v>
+      </c>
+      <c r="M49" s="3" t="n">
         <f aca="false">L49-(L49*0.1)</f>
-        <v>2473.416</v>
+        <v>776.898</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>15</v>
@@ -3090,635 +3321,430 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>166</v>
+        <v>31</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>155</v>
+        <v>390</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>155</v>
+        <v>430</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>455</v>
+        <v>275</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>415</v>
+        <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>415</v>
+        <v>220</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>140.7</v>
-      </c>
-      <c r="M50" s="2" t="n">
+        <v>240.96</v>
+      </c>
+      <c r="M50" s="3" t="n">
         <f aca="false">L50-(L50*0.1)</f>
-        <v>126.63</v>
+        <v>216.864</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>624</v>
+        <v>490</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>792</v>
+        <v>490</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>1367</v>
+        <v>350</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>0.7</v>
+        <v>1.95</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>5589.42</v>
-      </c>
-      <c r="M51" s="2" t="n">
+        <v>205.62</v>
+      </c>
+      <c r="M51" s="3" t="n">
         <f aca="false">L51-(L51*0.1)</f>
-        <v>5030.478</v>
+        <v>185.058</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>174</v>
+        <v>101010</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>415</v>
+        <v>100</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>3.7</v>
+        <v>100</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>3.7</v>
+        <v>100</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>415</v>
+        <v>100</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>6658.56</v>
-      </c>
-      <c r="M52" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3" t="n">
         <f aca="false">L52-(L52*0.1)</f>
-        <v>5992.704</v>
+        <v>90</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P52" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="G53" s="1" t="n">
+        <v>410</v>
+      </c>
+      <c r="H53" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H53" s="1" t="n">
-        <v>520</v>
-      </c>
       <c r="I53" s="1" t="n">
-        <v>790</v>
+        <v>300</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>4</v>
+        <v>45414</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>4</v>
+        <v>220</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>863.22</v>
-      </c>
-      <c r="M53" s="2" t="n">
+        <v>26708.04</v>
+      </c>
+      <c r="M53" s="3" t="n">
         <f aca="false">L53-(L53*0.1)</f>
-        <v>776.898</v>
+        <v>24037.236</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>430</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>370</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L54" s="1" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <f aca="false">L54-(L54*0.1)</f>
+        <v>19928.025</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="P54" s="1" t="n">
         <v>180</v>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>390</v>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>430</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>275</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>240.96</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <f aca="false">L54-(L54*0.1)</f>
-        <v>216.864</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O54" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="P54" s="1" t="n">
-        <v>90</v>
       </c>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>13</v>
+        <v>72</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>490</v>
+        <v>4300</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>490</v>
+        <v>3700</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>350</v>
+        <v>2100</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>205.62</v>
-      </c>
-      <c r="M55" s="2" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M55" s="3" t="n">
         <f aca="false">L55-(L55*0.1)</f>
-        <v>185.058</v>
+        <v>19928.025</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>101010</v>
-      </c>
-      <c r="D56" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>497</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>592</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>887</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>151889.52</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <f aca="false">L56-(L56*0.1)</f>
+        <v>136700.568</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P56" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="J56" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="K56" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="L56" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <f aca="false">L56-(L56*0.1)</f>
-        <v>90</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O56" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>45414</v>
+        <v>2.2</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>220</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>26708.04</v>
-      </c>
-      <c r="M57" s="2" t="n">
+        <v>22142.25</v>
+      </c>
+      <c r="M57" s="3" t="n">
         <f aca="false">L57-(L57*0.1)</f>
-        <v>24037.236</v>
+        <v>19928.025</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>430</v>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>370</v>
-      </c>
-      <c r="I58" s="1" t="n">
-        <v>210</v>
-      </c>
-      <c r="J58" s="1" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K58" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="L58" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M58" s="2" t="n">
-        <f aca="false">L58-(L58*0.1)</f>
-        <v>19928.025</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O58" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="H59" s="1" t="n">
-        <v>3700</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>2100</v>
-      </c>
-      <c r="J59" s="1" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="L59" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <f aca="false">L59-(L59*0.1)</f>
-        <v>19928.025</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O59" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>497</v>
-      </c>
-      <c r="H60" s="1" t="n">
-        <v>592</v>
-      </c>
-      <c r="I60" s="1" t="n">
-        <v>887</v>
-      </c>
-      <c r="J60" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K60" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="L60" s="1" t="n">
-        <v>151889.52</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <f aca="false">L60-(L60*0.1)</f>
-        <v>136700.568</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P60" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>430</v>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>370</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>210</v>
-      </c>
-      <c r="J61" s="1" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K61" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="L61" s="1" t="n">
-        <v>22142.25</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <f aca="false">L61-(L61*0.1)</f>
-        <v>19928.025</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1" display="https://file4"/>
-    <hyperlink ref="R2" r:id="rId2" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
-    <hyperlink ref="Q4" r:id="rId3" display="https://file4"/>
-    <hyperlink ref="R4" r:id="rId4" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
-    <hyperlink ref="Q6" r:id="rId5" display="https://file4.gif"/>
-    <hyperlink ref="R6" r:id="rId6" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="Q2" r:id="rId1" display="https://filestorage.com/123/document.pdf https://filestorage.com/123/instruction.doc https://file3.jpeg https://file4.gif"/>
+    <hyperlink ref="R2" r:id="rId2" display="https://imgur.com/123/картинка2.png https://imgur.com/123/картинка3.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="AA2" r:id="rId3" display="https://imgur.com/123/instruction.jpg https://imgur.com/123/картинка3.png"/>
+    <hyperlink ref="AB2" r:id="rId4" display="https://imgur.com/123/картинка2.png https://filestorage.com/123/instruction.doc"/>
+    <hyperlink ref="Q4" r:id="rId5" display="https://file1.jpg https://file2.png https://file3.jpeg https://file4.gif"/>
+    <hyperlink ref="R4" r:id="rId6" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
+    <hyperlink ref="Q6" r:id="rId7" display="https://file1.jpg https://file2.png https://file3.jpeg https://file4.gif"/>
+    <hyperlink ref="R6" r:id="rId8" display="https://picture1.jpg https://picture2.png https://picture3.jpeg https://picture4.gif"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
